--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106483</v>
+        <v>106494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 33277-2026 artfynd.xlsx
+++ b/artfynd/A 33277-2026 artfynd.xlsx
@@ -4542,7 +4542,7 @@
         <v>135958063</v>
       </c>
       <c r="B35" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
